--- a/budget-transfer/reference/17-calendar.xlsx
+++ b/budget-transfer/reference/17-calendar.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/budget-transfer/reference/17-calendar.xlsx
+++ b/budget-transfer/reference/17-calendar.xlsx
@@ -20,9 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -702,7 +703,7 @@
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
@@ -738,7 +739,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -769,7 +770,7 @@
     <row r="11" ht="30" customHeight="1" s="21">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>キックオフから一括移管までの締切と、定期作業の日程を管理する表。外部の基準日から逆算するイベントは「カレンダー」シートに、自らの決まりで実施日が決まる作業は「定期作業」シートに書く。</t>
+          <t>活動の開始から一括移管までの締切と、定期作業の日程を管理する表。外部の基準日から逆算するイベントは「カレンダー」シートに、自らの決まりで実施日が決まる作業は「定期作業」シートに書く。</t>
         </is>
       </c>
     </row>
@@ -899,7 +900,7 @@
     <row r="4" ht="15" customHeight="1" s="21">
       <c r="A4" s="33" t="inlineStr">
         <is>
-          <t>キックオフ</t>
+          <t>活動の開始</t>
         </is>
       </c>
       <c r="B4" s="50" t="n">
@@ -1139,12 +1140,12 @@
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>案件担当</t>
+          <t>窓口担当</t>
         </is>
       </c>
       <c r="D4" s="33" t="inlineStr">
         <is>
-          <t>キックオフ</t>
+          <t>活動の開始</t>
         </is>
       </c>
       <c r="E4" s="33" t="n">
@@ -1160,17 +1161,17 @@
       </c>
       <c r="H4" s="33" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="I4" s="33" t="inlineStr">
         <is>
-          <t>Runbook 案件担当編 §3.1</t>
+          <t>Runbook 窓口担当編 §3.1</t>
         </is>
       </c>
       <c r="J4" s="33" t="inlineStr">
         <is>
-          <t>2026-10-01。キックオフの前の事前の情報整理（決定記録「決定事項」No.33）</t>
+          <t>2026-10-01。活動の開始の前の事前の情報整理（決定記録「決定事項」No.33）</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1186,12 @@
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="D5" s="33" t="inlineStr">
         <is>
-          <t>キックオフ</t>
+          <t>活動の開始</t>
         </is>
       </c>
       <c r="E5" s="33" t="n">
@@ -1206,17 +1207,17 @@
       </c>
       <c r="H5" s="33" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="I5" s="33" t="inlineStr">
         <is>
-          <t>Runbook 進行役編 §3.3</t>
+          <t>Runbook 事務局編 §3.3</t>
         </is>
       </c>
       <c r="J5" s="33" t="inlineStr">
         <is>
-          <t>2026-10-30。予算移管の開始条件（キックオフまでに確定させる。決定事項 No.42）</t>
+          <t>2026-10-30。予算移管の開始条件（活動の開始までに確定させる。決定事項 No.42）</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1232,12 @@
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>案件担当</t>
+          <t>窓口担当</t>
         </is>
       </c>
       <c r="D6" s="33" t="inlineStr">
         <is>
-          <t>キックオフ</t>
+          <t>活動の開始</t>
         </is>
       </c>
       <c r="E6" s="33" t="n">
@@ -1252,12 +1253,12 @@
       </c>
       <c r="H6" s="33" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="I6" s="33" t="inlineStr">
         <is>
-          <t>Runbook 案件担当編 §3.1・§3.2</t>
+          <t>Runbook 窓口担当編 §3.1・§3.2</t>
         </is>
       </c>
       <c r="J6" s="33" t="inlineStr">
@@ -1272,7 +1273,7 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>キックオフ</t>
+          <t>活動の開始</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
@@ -1282,7 +1283,7 @@
       </c>
       <c r="D7" s="33" t="inlineStr">
         <is>
-          <t>キックオフ</t>
+          <t>活動の開始</t>
         </is>
       </c>
       <c r="E7" s="33" t="n">
@@ -1298,12 +1299,12 @@
       </c>
       <c r="H7" s="33" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="I7" s="33" t="inlineStr">
         <is>
-          <t>Runbook 進行役編 §3.1</t>
+          <t>Runbook 事務局編 §3.1</t>
         </is>
       </c>
       <c r="J7" s="33" t="n"/>
@@ -1314,7 +1315,7 @@
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>合意の期限</t>
+          <t>合意の目安</t>
         </is>
       </c>
       <c r="C8" s="33" t="inlineStr">
@@ -1340,12 +1341,12 @@
       </c>
       <c r="H8" s="33" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="I8" s="33" t="inlineStr">
         <is>
-          <t>Runbook 案件担当編 §3.4・§3.5</t>
+          <t>Runbook 窓口担当編 §3.4・§3.5</t>
         </is>
       </c>
       <c r="J8" s="33" t="inlineStr">
@@ -1360,12 +1361,12 @@
       </c>
       <c r="B9" s="33" t="inlineStr">
         <is>
-          <t>準備完了の確認の期限</t>
+          <t>準備完了の確認の目安</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
-          <t>案件担当</t>
+          <t>窓口担当</t>
         </is>
       </c>
       <c r="D9" s="33" t="inlineStr">
@@ -1386,12 +1387,12 @@
       </c>
       <c r="H9" s="33" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="I9" s="33" t="inlineStr">
         <is>
-          <t>Runbook 案件担当編 §3.7・§3.8</t>
+          <t>Runbook 窓口担当編 §3.7・§3.8</t>
         </is>
       </c>
       <c r="J9" s="33" t="inlineStr">
@@ -1432,12 +1433,12 @@
       </c>
       <c r="H10" s="33" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="I10" s="33" t="inlineStr">
         <is>
-          <t>Runbook 進行役編 §3.4</t>
+          <t>Runbook 事務局編 §3.4</t>
         </is>
       </c>
       <c r="J10" s="33" t="inlineStr">
@@ -1478,12 +1479,12 @@
       </c>
       <c r="H11" s="33" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="I11" s="33" t="inlineStr">
         <is>
-          <t>—（移管の稟議の承認の後。案件担当の作業はない）</t>
+          <t>—（移管の稟議の承認の後。窓口担当の作業はない）</t>
         </is>
       </c>
       <c r="J11" s="33" t="inlineStr">
@@ -1637,27 +1638,27 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>移管ステータスの確認（案件担当による見直しを含む）</t>
+          <t>移管ステータスの確認（窓口担当による見直しを含む）</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="D4" s="33" t="inlineStr">
         <is>
-          <t>毎日（案件担当が移管ステータスを随時更新する）</t>
+          <t>毎日（窓口担当が移管ステータスを随時更新する）</t>
         </is>
       </c>
       <c r="E4" s="33" t="inlineStr">
         <is>
-          <t>進行役が毎日、予算一覧を確かめる。部門の案件の移管ステータスが埋まったら移管の稟議を起票する</t>
+          <t>事務局が毎日、予算一覧を確かめる。部門の案件の移管ステータスが埋まったら移管の稟議を起票する</t>
         </is>
       </c>
       <c r="F4" s="33" t="inlineStr">
         <is>
-          <t>Runbook 進行役編 §3.6、案件担当編 §3.10</t>
+          <t>Runbook 事務局編 §3.6、窓口担当編 §3.10</t>
         </is>
       </c>
       <c r="G4" s="33" t="inlineStr">
@@ -1677,7 +1678,7 @@
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="D5" s="33" t="inlineStr">
@@ -1692,7 +1693,7 @@
       </c>
       <c r="F5" s="33" t="inlineStr">
         <is>
-          <t>Runbook 進行役編 §3.7</t>
+          <t>Runbook 事務局編 §3.7</t>
         </is>
       </c>
       <c r="G5" s="33" t="n"/>
@@ -1883,10 +1884,24 @@
       <c r="E8" s="33" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="21">
-      <c r="A9" s="33" t="n"/>
-      <c r="B9" s="33" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="33" t="n"/>
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B9" s="50" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>IT予算移管ガイドラインに合わせ、キックオフを活動の開始に、合意の期限・準備完了の確認の期限を目安に、進行役を事務局、案件担当を窓口担当に改めた</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>予算移管事務局</t>
+        </is>
+      </c>
       <c r="E9" s="33" t="n"/>
     </row>
   </sheetData>
